--- a/Schlagdifferentialgleichung/Programme/excelDir/CharactExponentenMultiplikatoren_ebeta0dot300_mu0_mu10_Auswahl7.xlsx
+++ b/Schlagdifferentialgleichung/Programme/excelDir/CharactExponentenMultiplikatoren_ebeta0dot300_mu0_mu10_Auswahl7.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -13,7 +13,241 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="104" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="91">
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
   <si>
     <t>muChar</t>
   </si>
@@ -57,7 +291,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -100,60 +334,60 @@
   <dimension ref="A1:M102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" customWidth="true"/>
-    <col min="2" max="2" width="13.21875" customWidth="true"/>
-    <col min="3" max="3" width="14.21875" customWidth="true"/>
-    <col min="4" max="4" width="15.21875" customWidth="true"/>
-    <col min="5" max="5" width="14.5546875" customWidth="true"/>
-    <col min="6" max="6" width="15.88671875" customWidth="true"/>
-    <col min="7" max="7" width="16.21875" customWidth="true"/>
-    <col min="8" max="8" width="15.21875" customWidth="true"/>
-    <col min="9" max="9" width="14.5546875" customWidth="true"/>
-    <col min="10" max="10" width="20.33203125" customWidth="true"/>
-    <col min="11" max="11" width="20.77734375" customWidth="true"/>
-    <col min="12" max="12" width="20.33203125" customWidth="true"/>
-    <col min="13" max="13" width="20.77734375" customWidth="true"/>
+    <col min="1" max="1" width="7.48828125" customWidth="true"/>
+    <col min="2" max="2" width="13.37890625" customWidth="true"/>
+    <col min="3" max="3" width="14.37890625" customWidth="true"/>
+    <col min="4" max="4" width="15.37890625" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" customWidth="true"/>
+    <col min="6" max="6" width="16.046875" customWidth="true"/>
+    <col min="7" max="7" width="16.37890625" customWidth="true"/>
+    <col min="8" max="8" width="15.37890625" customWidth="true"/>
+    <col min="9" max="9" width="14.7109375" customWidth="true"/>
+    <col min="10" max="10" width="20.48828125" customWidth="true"/>
+    <col min="11" max="11" width="20.93359375" customWidth="true"/>
+    <col min="12" max="12" width="20.48828125" customWidth="true"/>
+    <col min="13" max="13" width="20.93359375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2">
@@ -281,7 +515,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.30000000000000005</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="B5" s="0">
         <v>-0.3355326539048088</v>
@@ -311,13 +545,13 @@
         <v>-0.3355326539048088</v>
       </c>
       <c r="K5" s="0">
-        <v>-1.0567146859029784</v>
+        <v>-1.0567146859029783</v>
       </c>
       <c r="L5" s="0">
         <v>-0.33553265390480902</v>
       </c>
       <c r="M5" s="0">
-        <v>1.0567146859029784</v>
+        <v>1.0567146859029783</v>
       </c>
     </row>
     <row r="6">
@@ -460,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="0">
-        <v>0.070755184434576957</v>
+        <v>0.070755184434576956</v>
       </c>
       <c r="G9" s="0">
         <v>0.20848290838603117</v>
@@ -677,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="0">
-        <v>-0.58044829349194838</v>
+        <v>-0.58044829349194837</v>
       </c>
       <c r="K14" s="0">
         <v>-1</v>
@@ -861,7 +1095,7 @@
         <v>-0.76359330524949365</v>
       </c>
       <c r="C19" s="0">
-        <v>0.092527997439877025</v>
+        <v>0.092527997439877024</v>
       </c>
       <c r="D19" s="0">
         <v>0</v>
@@ -888,7 +1122,7 @@
         <v>-1</v>
       </c>
       <c r="L19" s="0">
-        <v>0.092527997439877025</v>
+        <v>0.092527997439877024</v>
       </c>
       <c r="M19" s="0">
         <v>1</v>
@@ -943,7 +1177,7 @@
         <v>-0.84358459906395278</v>
       </c>
       <c r="C21" s="0">
-        <v>0.1725192912543343</v>
+        <v>0.17251929125433429</v>
       </c>
       <c r="D21" s="0">
         <v>0</v>
@@ -970,7 +1204,7 @@
         <v>-1</v>
       </c>
       <c r="L21" s="0">
-        <v>0.1725192912543343</v>
+        <v>0.17251929125433429</v>
       </c>
       <c r="M21" s="0">
         <v>1</v>
@@ -1227,10 +1461,10 @@
         <v>2.6000000000000001</v>
       </c>
       <c r="B28" s="0">
-        <v>-1.1369736112191931</v>
+        <v>-1.136973611219193</v>
       </c>
       <c r="C28" s="0">
-        <v>0.46590830341171558</v>
+        <v>0.46590830341171557</v>
       </c>
       <c r="D28" s="0">
         <v>0</v>
@@ -1257,7 +1491,7 @@
         <v>-1</v>
       </c>
       <c r="L28" s="0">
-        <v>0.46590830341171558</v>
+        <v>0.46590830341171557</v>
       </c>
       <c r="M28" s="0">
         <v>1</v>
@@ -1350,7 +1584,7 @@
         <v>2.9000000000000004</v>
       </c>
       <c r="B31" s="0">
-        <v>-1.2542523252007754</v>
+        <v>-1.2542523252007753</v>
       </c>
       <c r="C31" s="0">
         <v>0.58318701737435485</v>
@@ -1637,7 +1871,7 @@
         <v>3.6000000000000001</v>
       </c>
       <c r="B38" s="0">
-        <v>-1.4579806494215411</v>
+        <v>-1.457980649421541</v>
       </c>
       <c r="C38" s="0">
         <v>0.78691534147235098</v>
@@ -1693,7 +1927,7 @@
         <v>9.5345618646547337e-05</v>
       </c>
       <c r="G39" s="0">
-        <v>154.7134189769393</v>
+        <v>154.71341897693929</v>
       </c>
       <c r="H39" s="0">
         <v>0</v>
@@ -1813,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="0">
-        <v>9.6043811389112666e-05</v>
+        <v>9.6043811389112665e-05</v>
       </c>
       <c r="G42" s="0">
         <v>153.58872602786317</v>
@@ -2047,7 +2281,7 @@
         <v>4.6000000000000005</v>
       </c>
       <c r="B48" s="0">
-        <v>1.0146538790901965</v>
+        <v>1.0146538790901964</v>
       </c>
       <c r="C48" s="0">
         <v>-1.6857191743804183</v>
@@ -2071,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="0">
-        <v>1.0146538790901965</v>
+        <v>1.0146538790901964</v>
       </c>
       <c r="K48" s="0">
         <v>-1.5</v>
@@ -2091,7 +2325,7 @@
         <v>1.0834367182848503</v>
       </c>
       <c r="C49" s="0">
-        <v>-1.7545020186685561</v>
+        <v>-1.754502018668556</v>
       </c>
       <c r="D49" s="0">
         <v>-0</v>
@@ -2118,7 +2352,7 @@
         <v>-1.5</v>
       </c>
       <c r="L49" s="0">
-        <v>-1.7545020260944682</v>
+        <v>-1.7545020260944681</v>
       </c>
       <c r="M49" s="0">
         <v>1.5</v>
@@ -2141,7 +2375,7 @@
         <v>-0</v>
       </c>
       <c r="F50" s="0">
-        <v>-1296.0662473735552</v>
+        <v>-1296.0662473735551</v>
       </c>
       <c r="G50" s="0">
         <v>-1.1381552894818014e-05</v>
@@ -2214,7 +2448,7 @@
         <v>1.230625505255964</v>
       </c>
       <c r="C52" s="0">
-        <v>-1.9016908356119005</v>
+        <v>-1.9016908356119004</v>
       </c>
       <c r="D52" s="0">
         <v>-0</v>
@@ -2349,7 +2583,7 @@
         <v>-3776.2920643750417</v>
       </c>
       <c r="G55" s="0">
-        <v>-3.9062774703779724e-06</v>
+        <v>-3.9062774703779723e-06</v>
       </c>
       <c r="H55" s="0">
         <v>0</v>
@@ -2510,7 +2744,7 @@
         <v>-0</v>
       </c>
       <c r="F59" s="0">
-        <v>-797.75434029311703</v>
+        <v>-797.75434029311702</v>
       </c>
       <c r="G59" s="0">
         <v>-1.8490963725525944e-05</v>
@@ -2563,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="0">
-        <v>-1.9284789789087376</v>
+        <v>-1.9284789789087375</v>
       </c>
       <c r="K60" s="0">
         <v>-2</v>
@@ -2659,7 +2893,7 @@
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>6.0999999999999997</v>
+        <v>6.0999999999999996</v>
       </c>
       <c r="B63" s="0">
         <v>-2.3078833824483929</v>
@@ -2864,7 +3098,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>6.5999999999999997</v>
+        <v>6.5999999999999996</v>
       </c>
       <c r="B68" s="0">
         <v>-2.6121128026210827</v>
@@ -2990,10 +3224,10 @@
         <v>6.9000000000000004</v>
       </c>
       <c r="B71" s="0">
-        <v>-2.7417056784281178</v>
+        <v>-2.7417056784281177</v>
       </c>
       <c r="C71" s="0">
-        <v>2.0718611782892134</v>
+        <v>2.0718611782892133</v>
       </c>
       <c r="D71" s="0">
         <v>0</v>
@@ -3005,7 +3239,7 @@
         <v>3.300374373793602e-08</v>
       </c>
       <c r="G71" s="0">
-        <v>450398.35970697017</v>
+        <v>450398.35970697016</v>
       </c>
       <c r="H71" s="0">
         <v>0</v>
@@ -3020,7 +3254,7 @@
         <v>-2</v>
       </c>
       <c r="L71" s="0">
-        <v>2.0718611782892134</v>
+        <v>2.0718611782892133</v>
       </c>
       <c r="M71" s="0">
         <v>2</v>
@@ -3069,7 +3303,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>7.0999999999999997</v>
+        <v>7.0999999999999996</v>
       </c>
       <c r="B73" s="0">
         <v>-2.8175793165308987</v>
@@ -3274,7 +3508,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>7.5999999999999997</v>
+        <v>7.5999999999999996</v>
       </c>
       <c r="B78" s="0">
         <v>-2.9554741675460288</v>
@@ -3479,7 +3713,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>8.0999999999999997</v>
+        <v>8.0999999999999996</v>
       </c>
       <c r="B83" s="0">
         <v>-2.8785344266433559</v>
@@ -3497,7 +3731,7 @@
         <v>1.3969838619232178e-08</v>
       </c>
       <c r="G83" s="0">
-        <v>1399331.7831438352</v>
+        <v>1399331.7831438351</v>
       </c>
       <c r="H83" s="0">
         <v>0</v>
@@ -3576,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="0">
-        <v>-1.2293457984924317e-07</v>
+        <v>-1.2293457984924316e-07</v>
       </c>
       <c r="G85" s="0">
         <v>64972.81631234847</v>
@@ -3684,7 +3918,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>8.5999999999999997</v>
+        <v>8.5999999999999996</v>
       </c>
       <c r="B88" s="0">
         <v>2.4442154119621748</v>
@@ -3887,7 +4121,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>9.0999999999999997</v>
+        <v>9.0999999999999996</v>
       </c>
       <c r="B93" s="0">
         <v>2.6759692981829022</v>
@@ -4086,7 +4320,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>9.5999999999999997</v>
+        <v>9.5999999999999996</v>
       </c>
       <c r="B98" s="0">
         <v>2.4561202372300177</v>
@@ -4208,7 +4442,7 @@
         <v>9.9000000000000004</v>
       </c>
       <c r="B101" s="0">
-        <v>-2.6934132257014412</v>
+        <v>-2.6934132257014411</v>
       </c>
       <c r="C101" s="0">
         <v>2.92494134091777</v>
